--- a/artfynd/A 18898-2025 artfynd.xlsx
+++ b/artfynd/A 18898-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123865762</v>
+        <v>123867103</v>
       </c>
       <c r="B2" t="n">
-        <v>57861</v>
+        <v>79869</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103015</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -713,27 +713,22 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Stortjärnberget, Jmt</t>
+          <t>Jorsänget, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>516412</v>
+        <v>516175</v>
       </c>
       <c r="R2" t="n">
-        <v>6950581</v>
+        <v>6950550</v>
       </c>
       <c r="S2" t="n">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -762,7 +757,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:19</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -772,7 +767,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:19</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -799,10 +794,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123867101</v>
+        <v>123868606</v>
       </c>
       <c r="B3" t="n">
-        <v>79773</v>
+        <v>79869</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -811,25 +806,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -846,13 +841,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>516175</v>
+        <v>516297</v>
       </c>
       <c r="R3" t="n">
-        <v>6950550</v>
+        <v>6950615</v>
       </c>
       <c r="S3" t="n">
-        <v>23</v>
+        <v>70</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -881,7 +876,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -891,7 +886,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -918,10 +913,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123867103</v>
+        <v>123868609</v>
       </c>
       <c r="B4" t="n">
-        <v>79869</v>
+        <v>98079</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -930,34 +925,39 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -965,13 +965,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>516175</v>
+        <v>516297</v>
       </c>
       <c r="R4" t="n">
-        <v>6950550</v>
+        <v>6950615</v>
       </c>
       <c r="S4" t="n">
-        <v>23</v>
+        <v>70</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1000,7 +1000,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1010,7 +1010,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>11:16</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ca 10 stänglar</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1037,10 +1042,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123868609</v>
+        <v>123865765</v>
       </c>
       <c r="B5" t="n">
-        <v>98079</v>
+        <v>91008</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1049,53 +1054,44 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Jorsänget, Jmt</t>
+          <t>Stortjärnberget, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>516297</v>
+        <v>516412</v>
       </c>
       <c r="R5" t="n">
-        <v>6950615</v>
+        <v>6950581</v>
       </c>
       <c r="S5" t="n">
-        <v>70</v>
+        <v>4</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1124,7 +1120,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1134,12 +1130,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:16</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ca 10 stänglar</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1166,10 +1157,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123865765</v>
+        <v>123867102</v>
       </c>
       <c r="B6" t="n">
-        <v>91008</v>
+        <v>79829</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1178,44 +1169,48 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>229497</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Stortjärnberget, Jmt</t>
+          <t>Jorsänget, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>516412</v>
+        <v>516175</v>
       </c>
       <c r="R6" t="n">
-        <v>6950581</v>
+        <v>6950550</v>
       </c>
       <c r="S6" t="n">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1244,7 +1239,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1254,7 +1249,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1281,10 +1276,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123867102</v>
+        <v>123865762</v>
       </c>
       <c r="B7" t="n">
-        <v>79829</v>
+        <v>57861</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1297,21 +1292,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>229497</v>
+        <v>103015</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1319,22 +1314,27 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Jorsänget, Jmt</t>
+          <t>Stortjärnberget, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>516175</v>
+        <v>516412</v>
       </c>
       <c r="R7" t="n">
-        <v>6950550</v>
+        <v>6950581</v>
       </c>
       <c r="S7" t="n">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1363,7 +1363,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1373,7 +1373,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1400,10 +1400,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123868608</v>
+        <v>123867101</v>
       </c>
       <c r="B8" t="n">
-        <v>96963</v>
+        <v>79773</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1416,21 +1416,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221941</v>
+        <v>6456</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1440,7 +1440,6 @@
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1448,13 +1447,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>516297</v>
+        <v>516175</v>
       </c>
       <c r="R8" t="n">
-        <v>6950615</v>
+        <v>6950550</v>
       </c>
       <c r="S8" t="n">
-        <v>70</v>
+        <v>23</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1483,7 +1482,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1493,7 +1492,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1520,10 +1519,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123868606</v>
+        <v>123868608</v>
       </c>
       <c r="B9" t="n">
-        <v>79869</v>
+        <v>96963</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1532,25 +1531,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>221941</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1560,6 +1559,7 @@
       </c>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>

--- a/artfynd/A 18898-2025 artfynd.xlsx
+++ b/artfynd/A 18898-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123868608</v>
+        <v>123865765</v>
       </c>
       <c r="B2" t="n">
-        <v>96985</v>
+        <v>91030</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,49 +687,44 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221941</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Jorsänget, Jmt</t>
+          <t>Stortjärnberget, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>516297</v>
+        <v>516412</v>
       </c>
       <c r="R2" t="n">
-        <v>6950615</v>
+        <v>6950581</v>
       </c>
       <c r="S2" t="n">
-        <v>70</v>
+        <v>4</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -758,7 +753,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -768,7 +763,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -795,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123867103</v>
+        <v>123867102</v>
       </c>
       <c r="B3" t="n">
-        <v>79891</v>
+        <v>79851</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,25 +802,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>229497</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -914,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123868609</v>
+        <v>123868606</v>
       </c>
       <c r="B4" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -926,39 +921,34 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -1012,11 +1002,6 @@
       <c r="AB4" t="inlineStr">
         <is>
           <t>11:16</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ca 10 stänglar</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1043,10 +1028,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123867102</v>
+        <v>123867101</v>
       </c>
       <c r="B5" t="n">
-        <v>79851</v>
+        <v>79795</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1059,21 +1044,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>229497</v>
+        <v>6456</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1162,10 +1147,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123868606</v>
+        <v>123865762</v>
       </c>
       <c r="B6" t="n">
-        <v>79891</v>
+        <v>57883</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1174,25 +1159,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>103015</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1200,22 +1185,27 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Jorsänget, Jmt</t>
+          <t>Stortjärnberget, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>516297</v>
+        <v>516412</v>
       </c>
       <c r="R6" t="n">
-        <v>6950615</v>
+        <v>6950581</v>
       </c>
       <c r="S6" t="n">
-        <v>70</v>
+        <v>4</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1244,7 +1234,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1254,7 +1244,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1281,10 +1271,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123865765</v>
+        <v>123868609</v>
       </c>
       <c r="B7" t="n">
-        <v>91030</v>
+        <v>98101</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1293,44 +1283,53 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Stortjärnberget, Jmt</t>
+          <t>Jorsänget, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>516412</v>
+        <v>516297</v>
       </c>
       <c r="R7" t="n">
-        <v>6950581</v>
+        <v>6950615</v>
       </c>
       <c r="S7" t="n">
-        <v>4</v>
+        <v>70</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1359,7 +1358,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1369,7 +1368,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>11:16</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ca 10 stänglar</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1396,10 +1400,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123865762</v>
+        <v>123868608</v>
       </c>
       <c r="B8" t="n">
-        <v>57883</v>
+        <v>96985</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1412,21 +1416,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103015</v>
+        <v>221941</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1434,27 +1438,23 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Stortjärnberget, Jmt</t>
+          <t>Jorsänget, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>516412</v>
+        <v>516297</v>
       </c>
       <c r="R8" t="n">
-        <v>6950581</v>
+        <v>6950615</v>
       </c>
       <c r="S8" t="n">
-        <v>4</v>
+        <v>70</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1483,7 +1483,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:19</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1493,7 +1493,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:19</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1520,10 +1520,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123867101</v>
+        <v>123867103</v>
       </c>
       <c r="B9" t="n">
-        <v>79795</v>
+        <v>79891</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1532,25 +1532,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">

--- a/artfynd/A 18898-2025 artfynd.xlsx
+++ b/artfynd/A 18898-2025 artfynd.xlsx
@@ -909,7 +909,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123868606</v>
+        <v>123867103</v>
       </c>
       <c r="B4" t="n">
         <v>79891</v>
@@ -956,13 +956,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>516297</v>
+        <v>516175</v>
       </c>
       <c r="R4" t="n">
-        <v>6950615</v>
+        <v>6950550</v>
       </c>
       <c r="S4" t="n">
-        <v>70</v>
+        <v>23</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -991,7 +991,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1001,7 +1001,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1028,10 +1028,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123867101</v>
+        <v>123865762</v>
       </c>
       <c r="B5" t="n">
-        <v>79795</v>
+        <v>57883</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1044,21 +1044,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6456</v>
+        <v>103015</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1066,22 +1066,27 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Jorsänget, Jmt</t>
+          <t>Stortjärnberget, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>516175</v>
+        <v>516412</v>
       </c>
       <c r="R5" t="n">
-        <v>6950550</v>
+        <v>6950581</v>
       </c>
       <c r="S5" t="n">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1110,7 +1115,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1120,7 +1125,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1147,10 +1152,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123865762</v>
+        <v>123868608</v>
       </c>
       <c r="B6" t="n">
-        <v>57883</v>
+        <v>96985</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1163,21 +1168,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103015</v>
+        <v>221941</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1185,27 +1190,23 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Stortjärnberget, Jmt</t>
+          <t>Jorsänget, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>516412</v>
+        <v>516297</v>
       </c>
       <c r="R6" t="n">
-        <v>6950581</v>
+        <v>6950615</v>
       </c>
       <c r="S6" t="n">
-        <v>4</v>
+        <v>70</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1234,7 +1235,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:19</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1244,7 +1245,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:19</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1271,10 +1272,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123868609</v>
+        <v>123867101</v>
       </c>
       <c r="B7" t="n">
-        <v>98101</v>
+        <v>79795</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1283,39 +1284,34 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>6456</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr"/>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1323,13 +1319,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>516297</v>
+        <v>516175</v>
       </c>
       <c r="R7" t="n">
-        <v>6950615</v>
+        <v>6950550</v>
       </c>
       <c r="S7" t="n">
-        <v>70</v>
+        <v>23</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1358,7 +1354,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1368,12 +1364,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:16</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ca 10 stänglar</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1400,10 +1391,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123868608</v>
+        <v>123868609</v>
       </c>
       <c r="B8" t="n">
-        <v>96985</v>
+        <v>98101</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1412,34 +1403,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
@@ -1494,6 +1489,11 @@
       <c r="AB8" t="inlineStr">
         <is>
           <t>11:16</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ca 10 stänglar</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1520,7 +1520,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123867103</v>
+        <v>123868606</v>
       </c>
       <c r="B9" t="n">
         <v>79891</v>
@@ -1567,13 +1567,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>516175</v>
+        <v>516297</v>
       </c>
       <c r="R9" t="n">
-        <v>6950550</v>
+        <v>6950615</v>
       </c>
       <c r="S9" t="n">
-        <v>23</v>
+        <v>70</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1602,7 +1602,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 18898-2025 artfynd.xlsx
+++ b/artfynd/A 18898-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123865765</v>
+        <v>123865762</v>
       </c>
       <c r="B2" t="n">
-        <v>91030</v>
+        <v>57883</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,30 +687,39 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>103015</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -753,7 +762,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -763,7 +772,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,10 +799,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123867102</v>
+        <v>123868608</v>
       </c>
       <c r="B3" t="n">
-        <v>79851</v>
+        <v>96985</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -806,21 +815,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>229497</v>
+        <v>221941</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,6 +839,7 @@
       </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -837,13 +847,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>516175</v>
+        <v>516297</v>
       </c>
       <c r="R3" t="n">
-        <v>6950550</v>
+        <v>6950615</v>
       </c>
       <c r="S3" t="n">
-        <v>23</v>
+        <v>70</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -872,7 +882,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -882,7 +892,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,7 +919,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123867103</v>
+        <v>123868606</v>
       </c>
       <c r="B4" t="n">
         <v>79891</v>
@@ -956,13 +966,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>516175</v>
+        <v>516297</v>
       </c>
       <c r="R4" t="n">
-        <v>6950550</v>
+        <v>6950615</v>
       </c>
       <c r="S4" t="n">
-        <v>23</v>
+        <v>70</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -991,7 +1001,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1001,7 +1011,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1028,10 +1038,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123865762</v>
+        <v>123865765</v>
       </c>
       <c r="B5" t="n">
-        <v>57883</v>
+        <v>91030</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1040,39 +1050,30 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103015</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1115,7 +1116,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:19</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1125,7 +1126,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:19</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1152,10 +1153,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123868608</v>
+        <v>123868609</v>
       </c>
       <c r="B6" t="n">
-        <v>96985</v>
+        <v>98101</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1164,34 +1165,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
@@ -1246,6 +1251,11 @@
       <c r="AB6" t="inlineStr">
         <is>
           <t>11:16</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ca 10 stänglar</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1391,10 +1401,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123868609</v>
+        <v>123867103</v>
       </c>
       <c r="B8" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1403,39 +1413,34 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1443,13 +1448,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>516297</v>
+        <v>516175</v>
       </c>
       <c r="R8" t="n">
-        <v>6950615</v>
+        <v>6950550</v>
       </c>
       <c r="S8" t="n">
-        <v>70</v>
+        <v>23</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1478,7 +1483,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1488,12 +1493,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:16</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ca 10 stänglar</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1520,10 +1520,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123868606</v>
+        <v>123867102</v>
       </c>
       <c r="B9" t="n">
-        <v>79891</v>
+        <v>79851</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1532,25 +1532,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>229497</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1567,13 +1567,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>516297</v>
+        <v>516175</v>
       </c>
       <c r="R9" t="n">
-        <v>6950615</v>
+        <v>6950550</v>
       </c>
       <c r="S9" t="n">
-        <v>70</v>
+        <v>23</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1602,7 +1602,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 18898-2025 artfynd.xlsx
+++ b/artfynd/A 18898-2025 artfynd.xlsx
@@ -919,10 +919,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123868606</v>
+        <v>123865765</v>
       </c>
       <c r="B4" t="n">
-        <v>79891</v>
+        <v>91030</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -935,44 +935,40 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Jorsänget, Jmt</t>
+          <t>Stortjärnberget, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>516297</v>
+        <v>516412</v>
       </c>
       <c r="R4" t="n">
-        <v>6950615</v>
+        <v>6950581</v>
       </c>
       <c r="S4" t="n">
-        <v>70</v>
+        <v>4</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1001,7 +997,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1011,7 +1007,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1038,10 +1034,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123865765</v>
+        <v>123868609</v>
       </c>
       <c r="B5" t="n">
-        <v>91030</v>
+        <v>98101</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1050,44 +1046,53 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Stortjärnberget, Jmt</t>
+          <t>Jorsänget, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>516412</v>
+        <v>516297</v>
       </c>
       <c r="R5" t="n">
-        <v>6950581</v>
+        <v>6950615</v>
       </c>
       <c r="S5" t="n">
-        <v>4</v>
+        <v>70</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1116,7 +1121,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1126,7 +1131,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>11:16</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ca 10 stänglar</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1153,10 +1163,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123868609</v>
+        <v>123867101</v>
       </c>
       <c r="B6" t="n">
-        <v>98101</v>
+        <v>79795</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1165,39 +1175,34 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>6456</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr"/>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1205,13 +1210,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>516297</v>
+        <v>516175</v>
       </c>
       <c r="R6" t="n">
-        <v>6950615</v>
+        <v>6950550</v>
       </c>
       <c r="S6" t="n">
-        <v>70</v>
+        <v>23</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1240,7 +1245,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1250,12 +1255,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:16</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ca 10 stänglar</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1282,10 +1282,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123867101</v>
+        <v>123867102</v>
       </c>
       <c r="B7" t="n">
-        <v>79795</v>
+        <v>79851</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1298,21 +1298,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6456</v>
+        <v>229497</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1401,7 +1401,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123867103</v>
+        <v>123868606</v>
       </c>
       <c r="B8" t="n">
         <v>79891</v>
@@ -1448,13 +1448,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>516175</v>
+        <v>516297</v>
       </c>
       <c r="R8" t="n">
-        <v>6950550</v>
+        <v>6950615</v>
       </c>
       <c r="S8" t="n">
-        <v>23</v>
+        <v>70</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1483,7 +1483,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1493,7 +1493,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1520,10 +1520,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123867102</v>
+        <v>123867103</v>
       </c>
       <c r="B9" t="n">
-        <v>79851</v>
+        <v>79891</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1532,25 +1532,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>229497</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">

--- a/artfynd/A 18898-2025 artfynd.xlsx
+++ b/artfynd/A 18898-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123865762</v>
+        <v>123867101</v>
       </c>
       <c r="B2" t="n">
-        <v>57883</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80336</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103015</v>
+        <v>6456</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -713,27 +708,22 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Stortjärnberget, Jmt</t>
+          <t>Jorsänget, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>516412</v>
+        <v>516175</v>
       </c>
       <c r="R2" t="n">
-        <v>6950581</v>
+        <v>6950550</v>
       </c>
       <c r="S2" t="n">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -762,7 +752,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:19</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -772,7 +762,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:19</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -799,37 +789,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123868608</v>
+        <v>123867103</v>
       </c>
       <c r="B3" t="n">
-        <v>96985</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221941</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -839,7 +824,6 @@
       </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -847,13 +831,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>516297</v>
+        <v>516175</v>
       </c>
       <c r="R3" t="n">
-        <v>6950615</v>
+        <v>6950550</v>
       </c>
       <c r="S3" t="n">
-        <v>70</v>
+        <v>23</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -882,7 +866,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -892,7 +876,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -919,15 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123865765</v>
+        <v>123868606</v>
       </c>
       <c r="B4" t="n">
-        <v>91030</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -935,40 +914,44 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Stortjärnberget, Jmt</t>
+          <t>Jorsänget, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>516412</v>
+        <v>516297</v>
       </c>
       <c r="R4" t="n">
-        <v>6950581</v>
+        <v>6950615</v>
       </c>
       <c r="S4" t="n">
-        <v>4</v>
+        <v>70</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -997,7 +980,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1007,7 +990,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1034,65 +1017,51 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123868609</v>
+        <v>124159870</v>
       </c>
       <c r="B5" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Jorsänget, Jmt</t>
+          <t>Lönningsberg, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>516297</v>
+        <v>516236</v>
       </c>
       <c r="R5" t="n">
-        <v>6950615</v>
+        <v>6950631</v>
       </c>
       <c r="S5" t="n">
-        <v>70</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1119,32 +1088,18 @@
           <t>2025-04-08</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>11:16</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-04-08</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>11:16</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ca 10 stänglar</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1163,15 +1118,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123867101</v>
+        <v>123865762</v>
       </c>
       <c r="B6" t="n">
-        <v>79795</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1179,21 +1129,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6456</v>
+        <v>103015</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1201,22 +1151,27 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Jorsänget, Jmt</t>
+          <t>Stortjärnberget, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>516175</v>
+        <v>516412</v>
       </c>
       <c r="R6" t="n">
-        <v>6950550</v>
+        <v>6950581</v>
       </c>
       <c r="S6" t="n">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1245,7 +1200,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1255,7 +1210,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1282,46 +1237,46 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123867102</v>
+        <v>123868609</v>
       </c>
       <c r="B7" t="n">
-        <v>79851</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>229497</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1329,13 +1284,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>516175</v>
+        <v>516297</v>
       </c>
       <c r="R7" t="n">
-        <v>6950550</v>
+        <v>6950615</v>
       </c>
       <c r="S7" t="n">
-        <v>23</v>
+        <v>70</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1364,7 +1319,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1374,7 +1329,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>11:16</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ca 10 stänglar</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1401,37 +1361,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123868606</v>
+        <v>123868608</v>
       </c>
       <c r="B8" t="n">
-        <v>79891</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97989</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>221941</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1441,6 +1396,7 @@
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1520,37 +1476,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123867103</v>
+        <v>123867102</v>
       </c>
       <c r="B9" t="n">
-        <v>79891</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80392</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>229497</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1636,112 +1587,6 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>124159870</v>
-      </c>
-      <c r="B10" t="n">
-        <v>79891</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>6458</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Lobaria pulmonaria</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>Lönningsberg, Jmt</t>
-        </is>
-      </c>
-      <c r="Q10" t="n">
-        <v>516236</v>
-      </c>
-      <c r="R10" t="n">
-        <v>6950631</v>
-      </c>
-      <c r="S10" t="n">
-        <v>10</v>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>Bräcke</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>Bodsjö</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>2025-04-08</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>2025-04-08</t>
-        </is>
-      </c>
-      <c r="AD10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF10" t="inlineStr"/>
-      <c r="AG10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT10" t="inlineStr"/>
-      <c r="AW10" t="inlineStr">
-        <is>
-          <t>Erik Söderhjelm</t>
-        </is>
-      </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>Erik Söderhjelm</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 18898-2025 artfynd.xlsx
+++ b/artfynd/A 18898-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1237,60 +1237,53 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123868609</v>
+        <v>134542220</v>
       </c>
       <c r="B7" t="n">
-        <v>99118</v>
+        <v>58136</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Jorsänget, Jmt</t>
+          <t>Jorsänget, Jorsänget, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>516297</v>
+        <v>516247</v>
       </c>
       <c r="R7" t="n">
-        <v>6950615</v>
+        <v>6950599</v>
       </c>
       <c r="S7" t="n">
-        <v>70</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1314,27 +1307,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>11:16</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>11:16</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ca 10 stänglar</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1349,53 +1327,57 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Erik Söderhjelm</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Erik Söderhjelm</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123868608</v>
+        <v>123868609</v>
       </c>
       <c r="B8" t="n">
-        <v>97989</v>
+        <v>99118</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
@@ -1450,6 +1432,11 @@
       <c r="AB8" t="inlineStr">
         <is>
           <t>11:16</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ca 10 stänglar</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1476,10 +1463,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123867102</v>
+        <v>123868608</v>
       </c>
       <c r="B9" t="n">
-        <v>80392</v>
+        <v>97989</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1487,21 +1474,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>229497</v>
+        <v>221941</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1511,6 +1498,7 @@
       </c>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1518,13 +1506,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>516175</v>
+        <v>516297</v>
       </c>
       <c r="R9" t="n">
-        <v>6950550</v>
+        <v>6950615</v>
       </c>
       <c r="S9" t="n">
-        <v>23</v>
+        <v>70</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1553,7 +1541,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1563,7 +1551,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1587,6 +1575,120 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>123867102</v>
+      </c>
+      <c r="B10" t="n">
+        <v>80392</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Jorsänget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>516175</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6950550</v>
+      </c>
+      <c r="S10" t="n">
+        <v>23</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Bodsjö</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-04-08</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>10:12</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-04-08</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>10:12</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Erik Söderhjelm</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Erik Söderhjelm</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
